--- a/output/看屋檢查清單_新北建案_2026-08-24_三_生活機能與交通.xlsx
+++ b/output/看屋檢查清單_新北建案_2026-08-24_三_生活機能與交通.xlsx
@@ -356,29 +356,8 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>環狀線景平站</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="001F4E78"/>
-              <sz val="10"/>
-            </rPr>
-            <t>共構</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>，出站即到家（步行0分鐘）
+          <t>環狀線景平站共構，出站即到家（步行0分鐘）
 可轉乘中和新蘆線與松山新店線</t>
-          </r>
         </is>
       </c>
     </row>
